--- a/aircraft/reports/sightings-over-time-yearly.xlsx
+++ b/aircraft/reports/sightings-over-time-yearly.xlsx
@@ -493,7 +493,7 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>2082</v>
+        <v>2087</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-yearly.xlsx
+++ b/aircraft/reports/sightings-over-time-yearly.xlsx
@@ -493,7 +493,7 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>2087</v>
+        <v>2088</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-yearly.xlsx
+++ b/aircraft/reports/sightings-over-time-yearly.xlsx
@@ -493,7 +493,7 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>2088</v>
+        <v>2082</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-yearly.xlsx
+++ b/aircraft/reports/sightings-over-time-yearly.xlsx
@@ -493,7 +493,7 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>2082</v>
+        <v>2089</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-yearly.xlsx
+++ b/aircraft/reports/sightings-over-time-yearly.xlsx
@@ -493,7 +493,7 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>2089</v>
+        <v>2108</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-yearly.xlsx
+++ b/aircraft/reports/sightings-over-time-yearly.xlsx
@@ -493,7 +493,7 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>2108</v>
+        <v>2120</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-yearly.xlsx
+++ b/aircraft/reports/sightings-over-time-yearly.xlsx
@@ -493,7 +493,7 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>2120</v>
+        <v>2136</v>
       </c>
     </row>
   </sheetData>
